--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_supbrut_a_2018_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_supbrut_a_2018_tarapaca.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:52</t>
+    <t xml:space="preserve">2026-09-24 00:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -672,7 +672,7 @@
         <v>-0.38</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>-0.3</v>
@@ -692,13 +692,13 @@
         <v>6</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.59</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="10">
@@ -718,7 +718,7 @@
         <v>-0.21</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>-0.22</v>
@@ -732,19 +732,19 @@
         <v>16</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
